--- a/test/1/Contingent.xlsx
+++ b/test/1/Contingent.xlsx
@@ -1,24 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B70646C-7685-488B-BFAD-001E5F84EF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21F84B0-6AFF-4D71-9BF9-9C072E3B6BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Приклад" sheetId="2" r:id="rId1"/>
-    <sheet name="ХХХ" sheetId="4" r:id="rId2"/>
+    <sheet name="Приклад" sheetId="3" r:id="rId1"/>
+    <sheet name="25-1" sheetId="2" r:id="rId2"/>
+    <sheet name="25-2" sheetId="4" r:id="rId3"/>
+    <sheet name="25-3" sheetId="5" r:id="rId4"/>
+    <sheet name="25-4" sheetId="6" r:id="rId5"/>
+    <sheet name="25-5" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="A1048577" localSheetId="1">#REF!</definedName>
+    <definedName name="A1048577" localSheetId="2">#REF!</definedName>
+    <definedName name="A1048577" localSheetId="3">#REF!</definedName>
+    <definedName name="A1048577" localSheetId="4">#REF!</definedName>
+    <definedName name="A1048577" localSheetId="5">#REF!</definedName>
     <definedName name="A1048577" localSheetId="0">#REF!</definedName>
-    <definedName name="A1048577" localSheetId="1">#REF!</definedName>
     <definedName name="A1048577">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Приклад!$C$3:$G$57</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">ХХХ!$C$3:$G$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'25-1'!$C$3:$G$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'25-2'!$C$3:$G$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'25-3'!$C$3:$G$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'25-4'!$C$3:$G$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'25-5'!$C$3:$G$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Приклад!$C$3:$G$46</definedName>
+    <definedName name="Ф80" localSheetId="1">#REF!</definedName>
+    <definedName name="Ф80" localSheetId="2">#REF!</definedName>
+    <definedName name="Ф80" localSheetId="3">#REF!</definedName>
+    <definedName name="Ф80" localSheetId="4">#REF!</definedName>
+    <definedName name="Ф80" localSheetId="5">#REF!</definedName>
     <definedName name="Ф80" localSheetId="0">#REF!</definedName>
-    <definedName name="Ф80" localSheetId="1">#REF!</definedName>
     <definedName name="Ф80">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="autoNoTable"/>
@@ -39,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="208">
   <si>
     <t>S</t>
   </si>
@@ -47,6 +63,16 @@
     <t>1 курс</t>
   </si>
   <si>
+    <t>Спеціальності G3 (141), G5 (172)</t>
+  </si>
+  <si>
+    <t>«Електрична інженерія»,
+«Електроніка, електронні комунікації, приладобудування та радіотехніка»</t>
+  </si>
+  <si>
+    <t>Група 25-4</t>
+  </si>
+  <si>
     <t>№</t>
   </si>
   <si>
@@ -59,10 +85,106 @@
     <t>Примітка</t>
   </si>
   <si>
+    <t>G3 (141)</t>
+  </si>
+  <si>
+    <t>Алексєєв Дмитро Олегович</t>
+  </si>
+  <si>
     <t>Б</t>
   </si>
   <si>
+    <t>Бойцов Олексій Валерійович</t>
+  </si>
+  <si>
     <t>К</t>
+  </si>
+  <si>
+    <t>Бурдіяк Ростислав Сергійович</t>
+  </si>
+  <si>
+    <t>Дехтяренко Станіслав Володимирович</t>
+  </si>
+  <si>
+    <t>Жуков Артем Андрійович</t>
+  </si>
+  <si>
+    <t>Змієвський Іван Максимович</t>
+  </si>
+  <si>
+    <t>Кисіль Артем Сергійович</t>
+  </si>
+  <si>
+    <t>Коваленко Володимир Олександрович</t>
+  </si>
+  <si>
+    <t>Ковтонюк Роман Сергійович</t>
+  </si>
+  <si>
+    <t>Кожукар Степан Степанович</t>
+  </si>
+  <si>
+    <t>Кукурінчук Євгеній Ігорович</t>
+  </si>
+  <si>
+    <t>Нєдов Дмитро Степанович</t>
+  </si>
+  <si>
+    <t>Ненашов Микола Валерійович</t>
+  </si>
+  <si>
+    <t>Петров Дмитро Ігорович</t>
+  </si>
+  <si>
+    <t>Рижкін Василь Петрович</t>
+  </si>
+  <si>
+    <t>Чебан Іван Іванович</t>
+  </si>
+  <si>
+    <t>Шереметьєв Владислав Артемович</t>
+  </si>
+  <si>
+    <t>G5 (172)</t>
+  </si>
+  <si>
+    <t>Висоцький Арсеній Андрійович</t>
+  </si>
+  <si>
+    <t>Дудник Михайло Олександрович</t>
+  </si>
+  <si>
+    <t>Кабанова Наталія Володимирівна</t>
+  </si>
+  <si>
+    <t>Косяк Антон Васильович</t>
+  </si>
+  <si>
+    <t>Ляшенко Данііл Євгенович</t>
+  </si>
+  <si>
+    <t>Мєржан Іван Віталійович</t>
+  </si>
+  <si>
+    <t>Половинко Костянтин Ігорович</t>
+  </si>
+  <si>
+    <t>Рзаєв Біннат Асеф огли</t>
+  </si>
+  <si>
+    <t>Сінькевич Назар Володимирович</t>
+  </si>
+  <si>
+    <t>Соколов Данііл Михайлович</t>
+  </si>
+  <si>
+    <t>Фомін Іван Олександрович</t>
+  </si>
+  <si>
+    <t>Ясюренко Михайло Сергійович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Класний керівник Возіян О.Г.</t>
   </si>
   <si>
     <r>
@@ -260,6 +382,318 @@
     <t>Шрамов`ят Михайло Ігорович</t>
   </si>
   <si>
+    <t>Бабков Дмитро Юрійович</t>
+  </si>
+  <si>
+    <t>Гальперина Анастасія Олексіївна</t>
+  </si>
+  <si>
+    <t>Григорашенко Олександра Олексіївна</t>
+  </si>
+  <si>
+    <t>Дмитришина Поліна Дмитрівна</t>
+  </si>
+  <si>
+    <t>Дмитрієв Міхаіл Олексійович</t>
+  </si>
+  <si>
+    <t>Здор Денис Володимирович</t>
+  </si>
+  <si>
+    <t>Карабай Діана Денисівна</t>
+  </si>
+  <si>
+    <t>Мельничук Даніїл Олександрович</t>
+  </si>
+  <si>
+    <t>Мусат Микола Володиславович</t>
+  </si>
+  <si>
+    <t>Подкопаєва Соф`я Андріївна</t>
+  </si>
+  <si>
+    <t>Пустовіт Дар`я Володимирівна</t>
+  </si>
+  <si>
+    <t>Стрельбицька Аліна Русланівна</t>
+  </si>
+  <si>
+    <t>Чобан Валерія Анатоліївна</t>
+  </si>
+  <si>
+    <t>Шапатіна Марія Олександрівна</t>
+  </si>
+  <si>
+    <t>Шингілєвич Станіслав Віталійович</t>
+  </si>
+  <si>
+    <t>Абаржі Юрій Петрович</t>
+  </si>
+  <si>
+    <t>Бондаренко Костянтин Петрович</t>
+  </si>
+  <si>
+    <t>Гавалко Єва Володимирівна</t>
+  </si>
+  <si>
+    <t>Гайдаржи Ілля Іванович</t>
+  </si>
+  <si>
+    <t>Господінов Дмитро Володимирович</t>
+  </si>
+  <si>
+    <t>Гроздя Роман Георгійович</t>
+  </si>
+  <si>
+    <t>Дончев Василь Васильович</t>
+  </si>
+  <si>
+    <t>Дюльгер Данііл Іванович</t>
+  </si>
+  <si>
+    <t>Коваленко Радислав Михайлович</t>
+  </si>
+  <si>
+    <t>Літвінов Давид Євгенович</t>
+  </si>
+  <si>
+    <t>Мазілін Іван Вікторович</t>
+  </si>
+  <si>
+    <t>Нейчев Сергій Федорович</t>
+  </si>
+  <si>
+    <t>Онофрійчук Андрій Миколайович</t>
+  </si>
+  <si>
+    <t>Письменний Кирило Віталійович</t>
+  </si>
+  <si>
+    <t>Семков Георгій Іванович</t>
+  </si>
+  <si>
+    <t>Сікорський Павло Євгенійович</t>
+  </si>
+  <si>
+    <t>Бахчиванжи Валентин Іванович</t>
+  </si>
+  <si>
+    <t>Верещагін Володимир Миколайович</t>
+  </si>
+  <si>
+    <t>Князян Карен Ашотович</t>
+  </si>
+  <si>
+    <t>Константинюк Іван Октавіанович</t>
+  </si>
+  <si>
+    <t>Група 25-2</t>
+  </si>
+  <si>
+    <t>Буюклі Христина Станіславівна</t>
+  </si>
+  <si>
+    <t>Голам-Сарвар Сабріна</t>
+  </si>
+  <si>
+    <t>Гусева Анна Олександрівна</t>
+  </si>
+  <si>
+    <t>Гуткан Алла Павлівна</t>
+  </si>
+  <si>
+    <t>Довгополий Олександр Анатолійович</t>
+  </si>
+  <si>
+    <t>Єсманчук Дмитро Сергійович</t>
+  </si>
+  <si>
+    <t>Загіченко Матвій Олександрович</t>
+  </si>
+  <si>
+    <t>Ляліна Дар`я Михайлівна</t>
+  </si>
+  <si>
+    <t>Марецький Максим Іванович</t>
+  </si>
+  <si>
+    <t>Савчук Станіслав Олександрович</t>
+  </si>
+  <si>
+    <t>Бондаренко Анна Юріївна</t>
+  </si>
+  <si>
+    <t>Бондаренко Олександр Сергійович</t>
+  </si>
+  <si>
+    <t>Грідін Олег Володимирович</t>
+  </si>
+  <si>
+    <t>Дімітрова Аделіна Віталіївна</t>
+  </si>
+  <si>
+    <t>Казанджій Гліб Миколайович</t>
+  </si>
+  <si>
+    <t>Олійник Олег Сергійович</t>
+  </si>
+  <si>
+    <t>Романчук Маргарита Вадимівна</t>
+  </si>
+  <si>
+    <t>Татарчук Антон Сергійович</t>
+  </si>
+  <si>
+    <t>Багаєв Дмитро Михайлович</t>
+  </si>
+  <si>
+    <t>Бєлов Миколай Михайлович</t>
+  </si>
+  <si>
+    <t>Богомолов Єгор Русланович</t>
+  </si>
+  <si>
+    <t>Горевой Костянтин Юрійович</t>
+  </si>
+  <si>
+    <t>Єлькін Владислав Леонідович</t>
+  </si>
+  <si>
+    <t>Капістеринський Ілля Сергійович</t>
+  </si>
+  <si>
+    <t>Краснов Кірілл Олександрович</t>
+  </si>
+  <si>
+    <t>Мельник Олександр Дмитрович</t>
+  </si>
+  <si>
+    <t>Півоварова Анастасія Володимирівна</t>
+  </si>
+  <si>
+    <t>Півоварова Олександра Володимирівна</t>
+  </si>
+  <si>
+    <t>Погребной Іван Олександрович</t>
+  </si>
+  <si>
+    <t>Русавський Максим Андрійович</t>
+  </si>
+  <si>
+    <t>Савкін Макар Максимович</t>
+  </si>
+  <si>
+    <t>Солтус Денис Віталійович</t>
+  </si>
+  <si>
+    <t>Стойков Дмитро Геннадійович</t>
+  </si>
+  <si>
+    <t>Чумляр Михайло Володимирович</t>
+  </si>
+  <si>
+    <t>Янчий Георгій Сергійович</t>
+  </si>
+  <si>
+    <t>Група 25-3</t>
+  </si>
+  <si>
+    <t>Білик Катерина Андріївна</t>
+  </si>
+  <si>
+    <t>Бондаренко Олександр Вікторович</t>
+  </si>
+  <si>
+    <t>Голуб Вероніка Русланівна</t>
+  </si>
+  <si>
+    <t>Гроза Вікторія Сергіївна</t>
+  </si>
+  <si>
+    <t>Денисенко Ярослав Денисович</t>
+  </si>
+  <si>
+    <t>Кловак Анастасія Ярославівна</t>
+  </si>
+  <si>
+    <t>Коцел Єгор Костянтинович</t>
+  </si>
+  <si>
+    <t>Крижньова Галина Олександрівна</t>
+  </si>
+  <si>
+    <t>Крівцова Анжеліка Олегівна</t>
+  </si>
+  <si>
+    <t>Кусенко Данило Сергійович</t>
+  </si>
+  <si>
+    <t>Місяць Олександра Миколаївна</t>
+  </si>
+  <si>
+    <t>Міхней Анна Олександрівна</t>
+  </si>
+  <si>
+    <t>Саркісова Олена Сергіївна</t>
+  </si>
+  <si>
+    <t>Кобелецька Ніколь Олегівна</t>
+  </si>
+  <si>
+    <t>Чернель Олександра Олегівна</t>
+  </si>
+  <si>
+    <t>Яковенко Крістіна Іванівна</t>
+  </si>
+  <si>
+    <t>Багнич Агата Валеріївна</t>
+  </si>
+  <si>
+    <t>Балабан Єлизавета Олексіївна</t>
+  </si>
+  <si>
+    <t>Басов Костянтин Юрійович</t>
+  </si>
+  <si>
+    <t>Бойко Станіслав Володимирович</t>
+  </si>
+  <si>
+    <t>Змашко Дар`я Сергіївна</t>
+  </si>
+  <si>
+    <t>Ілющенко Марія Володимирівна</t>
+  </si>
+  <si>
+    <t>Палій Маргарита Олександрівна</t>
+  </si>
+  <si>
+    <t>Померанцев Ілля Артурович</t>
+  </si>
+  <si>
+    <t>Торкатюк Ілля Сергійович</t>
+  </si>
+  <si>
+    <t>Чомов Максим Андрійович</t>
+  </si>
+  <si>
+    <t>Вілейко Вікторія Віленівна</t>
+  </si>
+  <si>
+    <t>Гуділіна Олександра Олександрівна</t>
+  </si>
+  <si>
+    <t>Сумець Вероніка Сергіївна</t>
+  </si>
+  <si>
+    <t>Тітаренко Маргарита Олександрівна</t>
+  </si>
+  <si>
+    <t>Шатілов Тимур Максимович</t>
+  </si>
+  <si>
+    <t>Група 25-5</t>
+  </si>
+  <si>
     <t>Спеціальності D5, E2, G13, J2, J3</t>
   </si>
   <si>
@@ -285,21 +719,49 @@
     <t>E2</t>
   </si>
   <si>
-    <t xml:space="preserve">    Класний керівник Вєра МЄШКОВА</t>
-  </si>
-  <si>
-    <t>Спеціальності ХХХ</t>
-  </si>
-  <si>
-    <t>ХХХ,
-ХХХ,
-ХХХ</t>
-  </si>
-  <si>
-    <t>Група ХХХ</t>
-  </si>
-  <si>
-    <t>ХХХ</t>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>G16</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>Спеціальності D7, G1, G16</t>
+  </si>
+  <si>
+    <t>«Торгівля»,
+«Хімічні технології та інженерія»,
+«Гірництво та нафтогазові технології»</t>
+  </si>
+  <si>
+    <t>Спеціальності E2, G1, G7</t>
+  </si>
+  <si>
+    <t>«Екологія»,
+«Хімічні технології та інженерія»,
+«Автоматизація, комп’ютерно-інтегровані технології та робототехніка»</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>Спеціальності G3, G5</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>Спеціальності G13, J2, J3</t>
+  </si>
+  <si>
+    <t>«Харчові технології»,
+«Готельно-ресторанна справа та кейтеринг»,
+«Туризм та рекреація»</t>
   </si>
   <si>
     <t xml:space="preserve">    Класний керівник </t>
@@ -631,7 +1093,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -724,27 +1186,23 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="7" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -763,6 +1221,16 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -802,7 +1270,7 @@
         <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F6C521D-63B8-4D90-998A-9000281454EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -811,7 +1279,7 @@
       <xdr:spPr>
         <a:xfrm flipH="1">
           <a:off x="4057650" y="1743075"/>
-          <a:ext cx="317789" cy="465483"/>
+          <a:ext cx="317789" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -856,14 +1324,14 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>3464</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>8283</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37A70654-B778-46FC-BDF1-2E4EF96E21B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -872,7 +1340,251 @@
       <xdr:spPr>
         <a:xfrm flipH="1">
           <a:off x="4057650" y="1743075"/>
-          <a:ext cx="317789" cy="427383"/>
+          <a:ext cx="317789" cy="465483"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3464</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4057650" y="2247900"/>
+          <a:ext cx="317789" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3464</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4057650" y="2247900"/>
+          <a:ext cx="317789" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3464</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4057650" y="1743075"/>
+          <a:ext cx="317789" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3464</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4057650" y="1552575"/>
+          <a:ext cx="317789" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1190,9 +1902,796 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH48"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="2.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="3" customWidth="1"/>
+    <col min="8" max="9" width="2.7109375" style="3" customWidth="1"/>
+    <col min="10" max="15" width="14.42578125" style="3" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="3" hidden="1" customWidth="1"/>
+    <col min="17" max="30" width="3.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="31" max="60" width="5.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="61" max="16384" width="14.42578125" style="3" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="162.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="8"/>
+    </row>
+    <row r="4" spans="1:9" s="11" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="17">
+        <v>1</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="8"/>
+    </row>
+    <row r="11" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="17">
+        <v>2</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="17">
+        <v>3</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="17">
+        <v>4</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="17">
+        <v>5</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="17">
+        <v>6</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="17">
+        <v>7</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="17">
+        <v>8</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="17">
+        <v>9</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="17">
+        <v>10</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="17">
+        <v>11</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="17">
+        <v>12</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="17">
+        <v>13</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="17">
+        <v>14</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="17">
+        <v>15</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="17">
+        <v>16</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="17">
+        <v>17</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="17">
+        <v>18</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="17">
+        <v>19</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="17">
+        <v>20</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="8"/>
+    </row>
+    <row r="31" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="17">
+        <v>21</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="8"/>
+    </row>
+    <row r="32" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="17">
+        <v>22</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="8"/>
+    </row>
+    <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="17">
+        <v>23</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="8"/>
+    </row>
+    <row r="34" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="17">
+        <v>24</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="17">
+        <v>25</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="17">
+        <v>26</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="8"/>
+    </row>
+    <row r="37" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="17">
+        <v>27</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="17">
+        <v>28</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="8"/>
+    </row>
+    <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="27">
+        <v>29</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="40" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="8"/>
+    </row>
+    <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="8"/>
+    </row>
+    <row r="42" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="8"/>
+    </row>
+    <row r="43" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="39" t="e">
+        <f ca="1">IF(COUNTBLANK(#REF!:OFFSET(C40,-1,0))&gt;0,"Очікую","Всього " &amp; COUNT(#REF!:OFFSET(C40,-1,0)) &amp; " студентів(а):")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E43" s="39"/>
+      <c r="F43" s="16" t="e">
+        <f ca="1">IF(D43="Очікую","Очікую","на контракті "&amp;COUNTIF(#REF!:OFFSET(E40,-1,0),"=К"))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G43" s="23"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="8"/>
+    </row>
+    <row r="44" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="8"/>
+    </row>
+    <row r="45" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16" t="e">
+        <f ca="1">IF(D43="Очікую","Очікую","на бюджеті "&amp;COUNTIF(#REF!:OFFSET(E40,-1,0),"=Б"))</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G45" s="23"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="8"/>
+    </row>
+    <row r="46" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="8"/>
+    </row>
+    <row r="47" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="8"/>
+    </row>
+    <row r="48" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="8"/>
+    </row>
+  </sheetData>
+  <sheetProtection insertRows="0" deleteRows="0"/>
+  <mergeCells count="12">
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="98" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF7030A0"/>
+    <tabColor rgb="FF0070C0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BH59"/>
@@ -1212,19 +2711,17 @@
     <col min="61" max="16384" width="14.42578125" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="159.94999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -1241,72 +2738,72 @@
     <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="C3" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="10"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" s="11" customFormat="1" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="C4" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="10"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="10"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="C6" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="10"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="29" t="s">
+      <c r="C7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>5</v>
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>8</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="8"/>
@@ -1314,26 +2811,26 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="37"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="10"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
+      <c r="C9" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="10"/>
       <c r="I9" s="8"/>
     </row>
@@ -1344,12 +2841,12 @@
         <v>1</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="27">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29">
         <v>40245</v>
       </c>
       <c r="G10" s="17"/>
@@ -1363,12 +2860,12 @@
         <v>2</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="27">
+        <v>11</v>
+      </c>
+      <c r="F11" s="29">
         <v>39942</v>
       </c>
       <c r="G11" s="17"/>
@@ -1382,12 +2879,12 @@
         <v>3</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="27">
+        <v>11</v>
+      </c>
+      <c r="F12" s="29">
         <v>40290</v>
       </c>
       <c r="G12" s="17"/>
@@ -1401,12 +2898,12 @@
         <v>4</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="27">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29">
         <v>40220</v>
       </c>
       <c r="G13" s="17"/>
@@ -1420,12 +2917,12 @@
         <v>5</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="27">
+        <v>11</v>
+      </c>
+      <c r="F14" s="29">
         <v>40346</v>
       </c>
       <c r="G14" s="17"/>
@@ -1439,12 +2936,12 @@
         <v>6</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="27">
+        <v>13</v>
+      </c>
+      <c r="F15" s="29">
         <v>40068</v>
       </c>
       <c r="G15" s="17"/>
@@ -1458,12 +2955,12 @@
         <v>7</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="27">
+        <v>11</v>
+      </c>
+      <c r="F16" s="29">
         <v>40418</v>
       </c>
       <c r="G16" s="17"/>
@@ -1477,12 +2974,12 @@
         <v>8</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="27">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29">
         <v>40296</v>
       </c>
       <c r="G17" s="17"/>
@@ -1496,12 +2993,12 @@
         <v>9</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="27">
+        <v>11</v>
+      </c>
+      <c r="F18" s="29">
         <v>40066</v>
       </c>
       <c r="G18" s="17"/>
@@ -1515,16 +3012,16 @@
         <v>10</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="27">
+        <v>11</v>
+      </c>
+      <c r="F19" s="29">
         <v>40165</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="8"/>
@@ -1536,12 +3033,12 @@
         <v>11</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="27">
+        <v>13</v>
+      </c>
+      <c r="F20" s="29">
         <v>40086</v>
       </c>
       <c r="G20" s="17"/>
@@ -1555,12 +3052,12 @@
         <v>12</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" s="27">
+        <v>11</v>
+      </c>
+      <c r="F21" s="29">
         <v>40341</v>
       </c>
       <c r="G21" s="17"/>
@@ -1574,12 +3071,12 @@
         <v>13</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="27">
+        <v>11</v>
+      </c>
+      <c r="F22" s="29">
         <v>40160</v>
       </c>
       <c r="G22" s="17"/>
@@ -1593,16 +3090,16 @@
         <v>14</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="27">
+        <v>11</v>
+      </c>
+      <c r="F23" s="29">
         <v>40055</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="8"/>
@@ -1614,12 +3111,12 @@
         <v>15</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="27">
+        <v>13</v>
+      </c>
+      <c r="F24" s="29">
         <v>39975</v>
       </c>
       <c r="G24" s="17"/>
@@ -1633,12 +3130,12 @@
         <v>16</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="27">
+        <v>11</v>
+      </c>
+      <c r="F25" s="29">
         <v>40057</v>
       </c>
       <c r="G25" s="17"/>
@@ -1652,12 +3149,12 @@
         <v>17</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" s="27">
+        <v>13</v>
+      </c>
+      <c r="F26" s="29">
         <v>40059</v>
       </c>
       <c r="G26" s="17"/>
@@ -1671,12 +3168,12 @@
         <v>18</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" s="27">
+        <v>11</v>
+      </c>
+      <c r="F27" s="29">
         <v>39944</v>
       </c>
       <c r="G27" s="17"/>
@@ -1690,12 +3187,12 @@
         <v>19</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" s="27">
+        <v>11</v>
+      </c>
+      <c r="F28" s="29">
         <v>40400</v>
       </c>
       <c r="G28" s="17"/>
@@ -1709,12 +3206,12 @@
         <v>20</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" s="27">
+        <v>11</v>
+      </c>
+      <c r="F29" s="29">
         <v>40246</v>
       </c>
       <c r="G29" s="17"/>
@@ -1724,13 +3221,13 @@
     <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
+      <c r="C30" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="10"/>
       <c r="I30" s="8"/>
     </row>
@@ -1741,12 +3238,12 @@
         <v>21</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="27">
+        <v>13</v>
+      </c>
+      <c r="F31" s="29">
         <v>28964</v>
       </c>
       <c r="G31" s="17"/>
@@ -1760,12 +3257,12 @@
         <v>22</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" s="27">
+        <v>13</v>
+      </c>
+      <c r="F32" s="29">
         <v>37547</v>
       </c>
       <c r="G32" s="17"/>
@@ -1779,12 +3276,12 @@
         <v>23</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" s="27">
+        <v>13</v>
+      </c>
+      <c r="F33" s="29">
         <v>29882</v>
       </c>
       <c r="G33" s="17"/>
@@ -1798,12 +3295,12 @@
         <v>24</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="27">
+        <v>13</v>
+      </c>
+      <c r="F34" s="29">
         <v>25471</v>
       </c>
       <c r="G34" s="17"/>
@@ -1817,12 +3314,12 @@
         <v>25</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="27">
+        <v>13</v>
+      </c>
+      <c r="F35" s="29">
         <v>29416</v>
       </c>
       <c r="G35" s="17"/>
@@ -1836,12 +3333,12 @@
         <v>26</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="27">
+        <v>13</v>
+      </c>
+      <c r="F36" s="29">
         <v>32150</v>
       </c>
       <c r="G36" s="17"/>
@@ -1855,12 +3352,12 @@
         <v>27</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="27">
+        <v>13</v>
+      </c>
+      <c r="F37" s="29">
         <v>32417</v>
       </c>
       <c r="G37" s="17"/>
@@ -1874,12 +3371,12 @@
         <v>28</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" s="27">
+        <v>13</v>
+      </c>
+      <c r="F38" s="29">
         <v>29045</v>
       </c>
       <c r="G38" s="17"/>
@@ -1893,12 +3390,12 @@
         <v>29</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="27">
+        <v>13</v>
+      </c>
+      <c r="F39" s="29">
         <v>31743</v>
       </c>
       <c r="G39" s="17"/>
@@ -1912,12 +3409,12 @@
         <v>30</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" s="27">
+        <v>13</v>
+      </c>
+      <c r="F40" s="29">
         <v>28236</v>
       </c>
       <c r="G40" s="17"/>
@@ -1931,12 +3428,12 @@
         <v>31</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" s="27">
+        <v>13</v>
+      </c>
+      <c r="F41" s="29">
         <v>27897</v>
       </c>
       <c r="G41" s="17"/>
@@ -1950,12 +3447,12 @@
         <v>32</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" s="27">
+        <v>13</v>
+      </c>
+      <c r="F42" s="29">
         <v>36506</v>
       </c>
       <c r="G42" s="17"/>
@@ -1969,12 +3466,12 @@
         <v>33</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="27">
+        <v>13</v>
+      </c>
+      <c r="F43" s="29">
         <v>27714</v>
       </c>
       <c r="G43" s="17"/>
@@ -1984,13 +3481,13 @@
     <row r="44" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
+      <c r="C44" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
       <c r="H44" s="10"/>
       <c r="I44" s="8"/>
     </row>
@@ -2001,12 +3498,12 @@
         <v>34</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" s="27"/>
+        <v>13</v>
+      </c>
+      <c r="F45" s="29"/>
       <c r="G45" s="17"/>
       <c r="H45" s="10"/>
       <c r="I45" s="8"/>
@@ -2014,13 +3511,13 @@
     <row r="46" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
+      <c r="C46" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
       <c r="H46" s="10"/>
       <c r="I46" s="8"/>
     </row>
@@ -2031,12 +3528,12 @@
         <v>35</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" s="27">
+        <v>13</v>
+      </c>
+      <c r="F47" s="29">
         <v>39898</v>
       </c>
       <c r="G47" s="17"/>
@@ -2046,13 +3543,13 @@
     <row r="48" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="9"/>
-      <c r="C48" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
+      <c r="C48" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
       <c r="H48" s="10"/>
       <c r="I48" s="8"/>
     </row>
@@ -2063,12 +3560,12 @@
         <v>36</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" s="27">
+        <v>13</v>
+      </c>
+      <c r="F49" s="29">
         <v>26625</v>
       </c>
       <c r="G49" s="17"/>
@@ -2082,12 +3579,12 @@
         <v>37</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" s="27"/>
+        <v>13</v>
+      </c>
+      <c r="F50" s="29"/>
       <c r="G50" s="17"/>
       <c r="H50" s="10"/>
       <c r="I50" s="8"/>
@@ -2107,11 +3604,11 @@
       <c r="A52" s="4"/>
       <c r="B52" s="9"/>
       <c r="C52" s="22"/>
-      <c r="D52" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
+      <c r="D52" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
       <c r="G52" s="23"/>
       <c r="H52" s="10"/>
       <c r="I52" s="8"/>
@@ -2131,11 +3628,11 @@
       <c r="A54" s="4"/>
       <c r="B54" s="9"/>
       <c r="C54" s="22"/>
-      <c r="D54" s="31" t="str">
+      <c r="D54" s="39" t="str">
         <f>IF(COUNTBLANK(C10:C50)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C50) &amp; " студентів(а):")</f>
         <v>Всього 37 студентів(а):</v>
       </c>
-      <c r="E54" s="31"/>
+      <c r="E54" s="39"/>
       <c r="F54" s="16" t="str">
         <f>IF(D54="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E50,"=К"))</f>
         <v>на контракті 21</v>
@@ -2204,8 +3701,13 @@
     </row>
   </sheetData>
   <sheetProtection insertRows="0" deleteRows="0"/>
-  <mergeCells count="16">
-    <mergeCell ref="B1:H1"/>
+  <mergeCells count="15">
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="D52:F52"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G4"/>
@@ -2215,12 +3717,6 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="D52:F52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
@@ -2229,13 +3725,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BH47"/>
+  <dimension ref="A1:BH55"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2.7109375" style="3" customWidth="1"/>
@@ -2279,72 +3775,72 @@
     <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="C3" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="10"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" s="11" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="C4" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="10"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="10"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="C6" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="10"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="29" t="s">
+      <c r="C7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>5</v>
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>8</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="8"/>
@@ -2352,26 +3848,26 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="37"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="10"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
+      <c r="C9" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="10"/>
       <c r="I9" s="8"/>
     </row>
@@ -2381,9 +3877,13 @@
       <c r="C10" s="17">
         <v>1</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="27"/>
+      <c r="D10" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29"/>
       <c r="G10" s="17"/>
       <c r="H10" s="10"/>
       <c r="I10" s="8"/>
@@ -2394,9 +3894,13 @@
       <c r="C11" s="17">
         <v>2</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="27"/>
+      <c r="D11" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="29"/>
       <c r="G11" s="17"/>
       <c r="H11" s="10"/>
       <c r="I11" s="8"/>
@@ -2407,9 +3911,13 @@
       <c r="C12" s="17">
         <v>3</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="27"/>
+      <c r="D12" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="29"/>
       <c r="G12" s="17"/>
       <c r="H12" s="10"/>
       <c r="I12" s="8"/>
@@ -2420,9 +3928,13 @@
       <c r="C13" s="17">
         <v>4</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="27"/>
+      <c r="D13" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29"/>
       <c r="G13" s="17"/>
       <c r="H13" s="10"/>
       <c r="I13" s="8"/>
@@ -2433,9 +3945,13 @@
       <c r="C14" s="17">
         <v>5</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="27"/>
+      <c r="D14" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="29"/>
       <c r="G14" s="17"/>
       <c r="H14" s="10"/>
       <c r="I14" s="8"/>
@@ -2443,13 +3959,17 @@
     <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="C15" s="17">
+        <v>6</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="17"/>
       <c r="H15" s="10"/>
       <c r="I15" s="8"/>
     </row>
@@ -2457,11 +3977,15 @@
       <c r="A16" s="4"/>
       <c r="B16" s="9"/>
       <c r="C16" s="17">
-        <v>5</v>
-      </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="27"/>
+        <v>7</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="29"/>
       <c r="G16" s="17"/>
       <c r="H16" s="10"/>
       <c r="I16" s="8"/>
@@ -2470,11 +3994,15 @@
       <c r="A17" s="4"/>
       <c r="B17" s="9"/>
       <c r="C17" s="17">
-        <v>6</v>
-      </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29"/>
       <c r="G17" s="17"/>
       <c r="H17" s="10"/>
       <c r="I17" s="8"/>
@@ -2483,11 +4011,15 @@
       <c r="A18" s="4"/>
       <c r="B18" s="9"/>
       <c r="C18" s="17">
-        <v>7</v>
-      </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="27"/>
+        <v>9</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="29"/>
       <c r="G18" s="17"/>
       <c r="H18" s="10"/>
       <c r="I18" s="8"/>
@@ -2496,11 +4028,15 @@
       <c r="A19" s="4"/>
       <c r="B19" s="9"/>
       <c r="C19" s="17">
-        <v>8</v>
-      </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="27"/>
+        <v>10</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="29"/>
       <c r="G19" s="17"/>
       <c r="H19" s="10"/>
       <c r="I19" s="8"/>
@@ -2509,11 +4045,15 @@
       <c r="A20" s="4"/>
       <c r="B20" s="9"/>
       <c r="C20" s="17">
-        <v>9</v>
-      </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="27"/>
+        <v>11</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="29"/>
       <c r="G20" s="17"/>
       <c r="H20" s="10"/>
       <c r="I20" s="8"/>
@@ -2521,13 +4061,17 @@
     <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
+      <c r="C21" s="17">
+        <v>12</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="17"/>
       <c r="H21" s="10"/>
       <c r="I21" s="8"/>
     </row>
@@ -2535,11 +4079,15 @@
       <c r="A22" s="4"/>
       <c r="B22" s="9"/>
       <c r="C22" s="17">
-        <v>10</v>
-      </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="27"/>
+        <v>13</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="29"/>
       <c r="G22" s="17"/>
       <c r="H22" s="10"/>
       <c r="I22" s="8"/>
@@ -2548,11 +4096,15 @@
       <c r="A23" s="4"/>
       <c r="B23" s="9"/>
       <c r="C23" s="17">
-        <v>11</v>
-      </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="27"/>
+        <v>14</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="29"/>
       <c r="G23" s="17"/>
       <c r="H23" s="10"/>
       <c r="I23" s="8"/>
@@ -2561,11 +4113,922 @@
       <c r="A24" s="4"/>
       <c r="B24" s="9"/>
       <c r="C24" s="17">
+        <v>15</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="17">
+        <v>16</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="17">
+        <v>17</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="29"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="17">
+        <v>18</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="17">
+        <v>19</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="8"/>
+    </row>
+    <row r="31" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="17">
+        <v>20</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="29">
+        <v>32690</v>
+      </c>
+      <c r="G31" s="17"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="8"/>
+    </row>
+    <row r="32" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="17">
+        <v>21</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="29">
+        <v>29727</v>
+      </c>
+      <c r="G32" s="17"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="8"/>
+    </row>
+    <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="17">
+        <v>22</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="8"/>
+    </row>
+    <row r="34" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="17">
+        <v>23</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="17">
+        <v>24</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="29">
+        <v>28919</v>
+      </c>
+      <c r="G35" s="17"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="17">
+        <v>25</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="8"/>
+    </row>
+    <row r="37" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="17">
+        <v>26</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="29"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="17">
+        <v>27</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="8"/>
+    </row>
+    <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="17">
+        <v>28</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="29">
+        <v>28346</v>
+      </c>
+      <c r="G39" s="17"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="40" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="17">
+        <v>29</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="29"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="8"/>
+    </row>
+    <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="17">
+        <v>30</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="29"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="8"/>
+    </row>
+    <row r="42" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="17">
+        <v>31</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="8"/>
+    </row>
+    <row r="43" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="17">
+        <v>32</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="29">
+        <v>32461</v>
+      </c>
+      <c r="G43" s="17"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="8"/>
+    </row>
+    <row r="44" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="17">
+        <v>33</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="29"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="8"/>
+    </row>
+    <row r="45" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="17">
+        <v>34</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="29"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="8"/>
+    </row>
+    <row r="46" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="17">
+        <v>35</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="8"/>
+    </row>
+    <row r="47" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="8"/>
+    </row>
+    <row r="48" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="8"/>
+    </row>
+    <row r="49" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="8"/>
+    </row>
+    <row r="50" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="39" t="str">
+        <f>IF(COUNTBLANK(C10:C46)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C46) &amp; " студентів(а):")</f>
+        <v>Всього 35 студентів(а):</v>
+      </c>
+      <c r="E50" s="39"/>
+      <c r="F50" s="16" t="str">
+        <f>IF(D50="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E46,"=К"))</f>
+        <v>на контракті 16</v>
+      </c>
+      <c r="G50" s="23"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="8"/>
+    </row>
+    <row r="51" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="8"/>
+    </row>
+    <row r="52" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16" t="str">
+        <f>IF(D50="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E46,"=Б"))</f>
+        <v>на бюджеті 19</v>
+      </c>
+      <c r="G52" s="23"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="8"/>
+    </row>
+    <row r="53" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="8"/>
+    </row>
+    <row r="54" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="4"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="8"/>
+    </row>
+    <row r="55" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="8"/>
+    </row>
+  </sheetData>
+  <sheetProtection insertRows="0" deleteRows="0"/>
+  <mergeCells count="13">
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH55"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="2.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="3" customWidth="1"/>
+    <col min="8" max="9" width="2.7109375" style="3" customWidth="1"/>
+    <col min="10" max="15" width="14.42578125" style="3" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="3" hidden="1" customWidth="1"/>
+    <col min="17" max="30" width="3.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="31" max="60" width="5.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="61" max="16384" width="14.42578125" style="3" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="8"/>
+    </row>
+    <row r="4" spans="1:9" s="11" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="17">
+        <v>1</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="8"/>
+    </row>
+    <row r="11" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="17">
+        <v>2</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="29"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="17">
+        <v>3</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="17">
+        <v>4</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="17">
+        <v>5</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="17">
+        <v>6</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="17">
+        <v>7</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="17">
+        <v>8</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="17">
+        <v>9</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="17">
+        <v>10</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="17">
+        <v>11</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="17">
         <v>12</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="27"/>
+      <c r="D22" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="29"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="17">
+        <v>13</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="29"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="17">
+        <v>14</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="29"/>
       <c r="G24" s="17"/>
       <c r="H24" s="10"/>
       <c r="I24" s="8"/>
@@ -2574,11 +5037,15 @@
       <c r="A25" s="4"/>
       <c r="B25" s="9"/>
       <c r="C25" s="17">
-        <v>13</v>
-      </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="27"/>
+        <v>15</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="29"/>
       <c r="G25" s="17"/>
       <c r="H25" s="10"/>
       <c r="I25" s="8"/>
@@ -2587,11 +5054,15 @@
       <c r="A26" s="4"/>
       <c r="B26" s="9"/>
       <c r="C26" s="17">
-        <v>14</v>
-      </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="27"/>
+        <v>16</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="29"/>
       <c r="G26" s="17"/>
       <c r="H26" s="10"/>
       <c r="I26" s="8"/>
@@ -2599,13 +5070,17 @@
     <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
+      <c r="C27" s="17">
+        <v>17</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="29"/>
+      <c r="G27" s="17"/>
       <c r="H27" s="10"/>
       <c r="I27" s="8"/>
     </row>
@@ -2613,11 +5088,916 @@
       <c r="A28" s="4"/>
       <c r="B28" s="9"/>
       <c r="C28" s="17">
+        <v>18</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="17">
+        <v>19</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="8"/>
+    </row>
+    <row r="31" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="17">
+        <v>20</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="29"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="8"/>
+    </row>
+    <row r="32" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="17">
+        <v>21</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="8"/>
+    </row>
+    <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="17">
+        <v>22</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="8"/>
+    </row>
+    <row r="34" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="17">
+        <v>23</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="17">
+        <v>24</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="29"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="17">
+        <v>25</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="8"/>
+    </row>
+    <row r="37" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="17">
+        <v>26</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="29"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="17">
+        <v>27</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="8"/>
+    </row>
+    <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="17">
+        <v>28</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="29"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="40" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="17">
+        <v>29</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="29"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="8"/>
+    </row>
+    <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="17">
+        <v>30</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="29"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="8"/>
+    </row>
+    <row r="42" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="17">
+        <v>31</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="8"/>
+    </row>
+    <row r="43" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="17">
+        <v>32</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="29"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="8"/>
+    </row>
+    <row r="44" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="17">
+        <v>33</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="29"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="8"/>
+    </row>
+    <row r="45" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="17">
+        <v>34</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="29"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="8"/>
+    </row>
+    <row r="46" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="17">
+        <v>35</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="8"/>
+    </row>
+    <row r="47" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="8"/>
+    </row>
+    <row r="48" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="8"/>
+    </row>
+    <row r="49" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="8"/>
+    </row>
+    <row r="50" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="39" t="str">
+        <f>IF(COUNTBLANK(C10:C46)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C46) &amp; " студентів(а):")</f>
+        <v>Всього 35 студентів(а):</v>
+      </c>
+      <c r="E50" s="39"/>
+      <c r="F50" s="16" t="str">
+        <f>IF(D50="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E46,"=К"))</f>
+        <v>на контракті 6</v>
+      </c>
+      <c r="G50" s="23"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="8"/>
+    </row>
+    <row r="51" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="8"/>
+    </row>
+    <row r="52" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16" t="str">
+        <f>IF(D50="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E46,"=Б"))</f>
+        <v>на бюджеті 29</v>
+      </c>
+      <c r="G52" s="23"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="8"/>
+    </row>
+    <row r="53" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="8"/>
+    </row>
+    <row r="54" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="4"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="8"/>
+    </row>
+    <row r="55" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="8"/>
+    </row>
+  </sheetData>
+  <sheetProtection insertRows="0" deleteRows="0"/>
+  <mergeCells count="13">
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH48"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="2.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="3" customWidth="1"/>
+    <col min="8" max="9" width="2.7109375" style="3" customWidth="1"/>
+    <col min="10" max="15" width="14.42578125" style="3" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="3" hidden="1" customWidth="1"/>
+    <col min="17" max="30" width="3.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="31" max="60" width="5.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="61" max="16384" width="14.42578125" style="3" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="8"/>
+    </row>
+    <row r="4" spans="1:9" s="11" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="17">
+        <v>1</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="8"/>
+    </row>
+    <row r="11" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="17">
+        <v>2</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="29"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="17">
+        <v>3</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="17">
+        <v>4</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="27"/>
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="17">
+        <v>5</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="17">
+        <v>6</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="17">
+        <v>7</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="17">
+        <v>8</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="17">
+        <v>9</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="17">
+        <v>10</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="17">
+        <v>11</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="29"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="17">
+        <v>12</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="17">
+        <v>13</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="29"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="17">
+        <v>14</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="29"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="17">
+        <v>15</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="17">
+        <v>16</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="29"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="17">
+        <v>17</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="17">
+        <v>18</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="29"/>
       <c r="G28" s="17"/>
       <c r="H28" s="10"/>
       <c r="I28" s="8"/>
@@ -2626,11 +6006,15 @@
       <c r="A29" s="4"/>
       <c r="B29" s="9"/>
       <c r="C29" s="17">
-        <v>16</v>
-      </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="27"/>
+        <v>19</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="29"/>
       <c r="G29" s="17"/>
       <c r="H29" s="10"/>
       <c r="I29" s="8"/>
@@ -2639,11 +6023,15 @@
       <c r="A30" s="4"/>
       <c r="B30" s="9"/>
       <c r="C30" s="17">
-        <v>17</v>
-      </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="27"/>
+        <v>20</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="29"/>
       <c r="G30" s="17"/>
       <c r="H30" s="10"/>
       <c r="I30" s="8"/>
@@ -2652,11 +6040,15 @@
       <c r="A31" s="4"/>
       <c r="B31" s="9"/>
       <c r="C31" s="17">
-        <v>18</v>
-      </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="27"/>
+        <v>21</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="29"/>
       <c r="G31" s="17"/>
       <c r="H31" s="10"/>
       <c r="I31" s="8"/>
@@ -2665,11 +6057,15 @@
       <c r="A32" s="4"/>
       <c r="B32" s="9"/>
       <c r="C32" s="17">
-        <v>19</v>
-      </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="27"/>
+        <v>22</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="29"/>
       <c r="G32" s="17"/>
       <c r="H32" s="10"/>
       <c r="I32" s="8"/>
@@ -2677,13 +6073,17 @@
     <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
+      <c r="C33" s="17">
+        <v>23</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="17"/>
       <c r="H33" s="10"/>
       <c r="I33" s="8"/>
     </row>
@@ -2691,11 +6091,15 @@
       <c r="A34" s="4"/>
       <c r="B34" s="9"/>
       <c r="C34" s="17">
-        <v>20</v>
-      </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="27"/>
+        <v>24</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="29"/>
       <c r="G34" s="17"/>
       <c r="H34" s="10"/>
       <c r="I34" s="8"/>
@@ -2704,11 +6108,15 @@
       <c r="A35" s="4"/>
       <c r="B35" s="9"/>
       <c r="C35" s="17">
-        <v>21</v>
-      </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="27"/>
+        <v>25</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="29"/>
       <c r="G35" s="17"/>
       <c r="H35" s="10"/>
       <c r="I35" s="8"/>
@@ -2717,11 +6125,15 @@
       <c r="A36" s="4"/>
       <c r="B36" s="9"/>
       <c r="C36" s="17">
-        <v>22</v>
-      </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="27"/>
+        <v>26</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="29"/>
       <c r="G36" s="17"/>
       <c r="H36" s="10"/>
       <c r="I36" s="8"/>
@@ -2730,11 +6142,15 @@
       <c r="A37" s="4"/>
       <c r="B37" s="9"/>
       <c r="C37" s="17">
-        <v>23</v>
-      </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="27"/>
+        <v>27</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="29"/>
       <c r="G37" s="17"/>
       <c r="H37" s="10"/>
       <c r="I37" s="8"/>
@@ -2743,147 +6159,998 @@
       <c r="A38" s="4"/>
       <c r="B38" s="9"/>
       <c r="C38" s="17">
-        <v>24</v>
-      </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="27"/>
+        <v>28</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="29"/>
       <c r="G38" s="17"/>
       <c r="H38" s="10"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="21"/>
+      <c r="C39" s="17">
+        <v>29</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="29"/>
+      <c r="G39" s="17"/>
       <c r="H39" s="10"/>
       <c r="I39" s="8"/>
     </row>
-    <row r="40" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="23"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="21"/>
       <c r="H40" s="10"/>
       <c r="I40" s="8"/>
     </row>
-    <row r="41" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="9"/>
       <c r="C41" s="22"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
+      <c r="D41" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
       <c r="G41" s="23"/>
       <c r="H41" s="10"/>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
       <c r="C42" s="22"/>
-      <c r="D42" s="31" t="str">
-        <f>IF(COUNTBLANK(C10:C38)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C38) &amp; " студентів(а):")</f>
-        <v>Всього 25 студентів(а):</v>
-      </c>
-      <c r="E42" s="31"/>
-      <c r="F42" s="16" t="str">
-        <f>IF(D42="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E38,"=К"))</f>
-        <v>на контракті 0</v>
-      </c>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
       <c r="G42" s="23"/>
       <c r="H42" s="10"/>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
       <c r="C43" s="22"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
+      <c r="D43" s="39" t="str">
+        <f>IF(COUNTBLANK(C10:C39)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C39) &amp; " студентів(а):")</f>
+        <v>Всього 29 студентів(а):</v>
+      </c>
+      <c r="E43" s="39"/>
+      <c r="F43" s="16" t="str">
+        <f>IF(D43="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E39,"=К"))</f>
+        <v>на контракті 8</v>
+      </c>
       <c r="G43" s="23"/>
       <c r="H43" s="10"/>
       <c r="I43" s="8"/>
     </row>
-    <row r="44" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
       <c r="C44" s="22"/>
       <c r="D44" s="15"/>
       <c r="E44" s="15"/>
-      <c r="F44" s="16" t="str">
-        <f>IF(D42="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E38,"=Б"))</f>
-        <v>на бюджеті 0</v>
-      </c>
+      <c r="F44" s="15"/>
       <c r="G44" s="23"/>
       <c r="H44" s="10"/>
       <c r="I44" s="8"/>
     </row>
-    <row r="45" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="26"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16" t="str">
+        <f>IF(D43="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E39,"=Б"))</f>
+        <v>на бюджеті 21</v>
+      </c>
+      <c r="G45" s="23"/>
       <c r="H45" s="10"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="14"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="10"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
+    <row r="47" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="14"/>
       <c r="I47" s="8"/>
+    </row>
+    <row r="48" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="8"/>
     </row>
   </sheetData>
   <sheetProtection insertRows="0" deleteRows="0"/>
-  <mergeCells count="15">
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D40:F40"/>
+  <mergeCells count="12">
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D41:F41"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C9:G9"/>
     <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="C7:C8"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH51"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="2.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="3" customWidth="1"/>
+    <col min="8" max="9" width="2.7109375" style="3" customWidth="1"/>
+    <col min="10" max="15" width="14.42578125" style="3" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="3" hidden="1" customWidth="1"/>
+    <col min="17" max="30" width="3.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="31" max="60" width="5.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="61" max="16384" width="14.42578125" style="3" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="8"/>
+    </row>
+    <row r="4" spans="1:9" s="11" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="17">
+        <v>1</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="8"/>
+    </row>
+    <row r="11" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="17">
+        <v>2</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="29"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="17">
+        <v>3</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="17">
+        <v>4</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="17">
+        <v>5</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="17">
+        <v>6</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="17">
+        <v>7</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="17">
+        <v>8</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="17">
+        <v>9</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="17">
+        <v>10</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="17">
+        <v>11</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="29"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="17">
+        <v>12</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="17">
+        <v>13</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="29"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="17">
+        <v>14</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="17">
+        <v>15</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="29"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="17">
+        <v>16</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="17">
+        <v>17</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="29"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="17">
+        <v>18</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="17">
+        <v>19</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="17">
+        <v>20</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="8"/>
+    </row>
+    <row r="31" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="17">
+        <v>21</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="29"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="8"/>
+    </row>
+    <row r="32" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="17">
+        <v>22</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="8"/>
+    </row>
+    <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="17">
+        <v>23</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="8"/>
+    </row>
+    <row r="34" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="17">
+        <v>24</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="17">
+        <v>25</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="29"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="17">
+        <v>26</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="8"/>
+    </row>
+    <row r="37" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="17">
+        <v>27</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="8"/>
+    </row>
+    <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="17">
+        <v>28</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="29"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="40" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="17">
+        <v>29</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="29"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="8"/>
+    </row>
+    <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="17">
+        <v>30</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="29"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="8"/>
+    </row>
+    <row r="42" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="17">
+        <v>31</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="8"/>
+    </row>
+    <row r="43" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="8"/>
+    </row>
+    <row r="44" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="8"/>
+    </row>
+    <row r="45" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="8"/>
+    </row>
+    <row r="46" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="39" t="str">
+        <f>IF(COUNTBLANK(C10:C42)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C42) &amp; " студентів(а):")</f>
+        <v>Всього 31 студентів(а):</v>
+      </c>
+      <c r="E46" s="39"/>
+      <c r="F46" s="16" t="str">
+        <f>IF(D46="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E42,"=К"))</f>
+        <v>на контракті 18</v>
+      </c>
+      <c r="G46" s="23"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="8"/>
+    </row>
+    <row r="47" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="8"/>
+    </row>
+    <row r="48" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16" t="str">
+        <f>IF(D46="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E42,"=Б"))</f>
+        <v>на бюджеті 13</v>
+      </c>
+      <c r="G48" s="23"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="8"/>
+    </row>
+    <row r="49" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="8"/>
+    </row>
+    <row r="50" spans="1:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="8"/>
+    </row>
+    <row r="51" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="8"/>
+    </row>
+  </sheetData>
+  <sheetProtection insertRows="0" deleteRows="0"/>
+  <mergeCells count="13">
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>